--- a/data/EOBFC fines list 25_26.xlsx
+++ b/data/EOBFC fines list 25_26.xlsx
@@ -17,7 +17,7 @@
     <sheet state="visible" name="GW12" sheetId="12" r:id="rId16"/>
     <sheet state="visible" name="GW13" sheetId="13" r:id="rId17"/>
     <sheet state="visible" name="GW14" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="GW15 " sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="GW15" sheetId="15" r:id="rId19"/>
     <sheet state="visible" name="GW16" sheetId="16" r:id="rId20"/>
     <sheet state="visible" name="GW17" sheetId="17" r:id="rId21"/>
     <sheet state="visible" name="GW18" sheetId="18" r:id="rId22"/>
@@ -465,7 +465,7 @@
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="GW15 -style">
+    <tableStyle count="3" pivot="0" name="GW15-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -803,7 +803,7 @@
     <tableColumn name="Alex Graham" id="23"/>
     <tableColumn name="Darren Ofoe" id="24"/>
   </tableColumns>
-  <tableStyleInfo name="GW15 -style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="GW15-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
